--- a/DahlaFlowerShop/test/AutomationFramework/testdata/test_data.xlsx
+++ b/DahlaFlowerShop/test/AutomationFramework/testdata/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T14s-Gen1\Desktop\DATN\DahlaFlowerShop\test\AutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB6C5CC-36C8-4EE2-B1EC-CD1D511D5AD7}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B4B0B8-7BFC-4E09-A442-643323E189D6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="330">
   <si>
     <t>id</t>
   </si>
@@ -540,9 +540,6 @@
     <t>Username chứa ký tự đặc biệt</t>
   </si>
   <si>
-    <t>adm!n</t>
-  </si>
-  <si>
     <t>L17</t>
   </si>
   <si>
@@ -558,12 +555,6 @@
     <t>L19</t>
   </si>
   <si>
-    <t>Username quá dài</t>
-  </si>
-  <si>
-    <t>adminadminadminadmin</t>
-  </si>
-  <si>
     <t>L20</t>
   </si>
   <si>
@@ -585,12 +576,6 @@
     <t>L22</t>
   </si>
   <si>
-    <t>Username có dấu tiếng Việt</t>
-  </si>
-  <si>
-    <t>admín</t>
-  </si>
-  <si>
     <t>L23</t>
   </si>
   <si>
@@ -639,103 +624,28 @@
     <t>L28</t>
   </si>
   <si>
-    <t>Username null</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>L29</t>
-  </si>
-  <si>
-    <t>Password null</t>
-  </si>
-  <si>
-    <t>L30</t>
-  </si>
-  <si>
-    <t>Username và password null</t>
-  </si>
-  <si>
-    <t>L31</t>
-  </si>
-  <si>
-    <t>Username chứa emoji</t>
-  </si>
-  <si>
-    <t>admin😀</t>
-  </si>
-  <si>
-    <t>L32</t>
-  </si>
-  <si>
-    <t>Password chứa emoji</t>
-  </si>
-  <si>
-    <t>pass😀123</t>
-  </si>
-  <si>
-    <t>L33</t>
-  </si>
-  <si>
-    <t>Username chỉ chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>" "</t>
-  </si>
-  <si>
-    <t>L34</t>
-  </si>
-  <si>
-    <t>Password chỉ chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>L35</t>
-  </si>
-  <si>
     <t>Username có tab</t>
   </si>
   <si>
     <t>admin\t</t>
   </si>
   <si>
-    <t>L36</t>
-  </si>
-  <si>
     <t>Password có tab</t>
   </si>
   <si>
     <t>123\t</t>
   </si>
   <si>
-    <t>L37</t>
-  </si>
-  <si>
     <t>Username có xuống dòng</t>
   </si>
   <si>
     <t>admin\n</t>
   </si>
   <si>
-    <t>L38</t>
-  </si>
-  <si>
     <t>Password có xuống dòng</t>
   </si>
   <si>
     <t>123\n</t>
-  </si>
-  <si>
-    <t>L39</t>
-  </si>
-  <si>
-    <t>Ký tự Unicode trong username</t>
-  </si>
-  <si>
-    <t>用户名</t>
-  </si>
-  <si>
-    <t>L40</t>
   </si>
   <si>
     <t>Ký tự Unicode trong password</t>
@@ -1512,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1667,7 +1577,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>154</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1684,7 +1594,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>157</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1701,7 +1611,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>160</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1718,7 +1628,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1735,7 +1645,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>164</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1752,7 +1662,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1769,7 +1679,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1786,427 +1696,223 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>170</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1.23456789012345E+19</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="4">
+      <c r="B18" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" s="4">
         <v>123</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="E18" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="B19" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="4">
-        <v>1.23456789012345E+19</v>
+      <c r="D19" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D20" s="4">
-        <v>123</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>180</v>
-      </c>
       <c r="B21" s="4" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D21" s="4">
         <v>123</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>9</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>183</v>
+      <c r="A22" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>9</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>186</v>
+      <c r="A23" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D23" s="4">
         <v>123</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>12</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>189</v>
+      <c r="A24" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>9</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>192</v>
+      <c r="A25" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D25" s="4">
         <v>123</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>196</v>
+      <c r="A26" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>198</v>
+      <c r="A27" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D27" s="4">
         <v>123</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>201</v>
+      <c r="A28" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>204</v>
+      <c r="A29" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="4">
-        <v>123</v>
+        <v>7</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>209</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D32" s="4">
-        <v>123</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D34" s="4">
-        <v>123</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D36" s="4">
-        <v>123</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D38" s="4">
-        <v>123</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D40" s="4">
-        <v>123</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E41" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2519,10 +2225,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>7</v>
@@ -2531,10 +2237,10 @@
         <v>40</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="G10" s="6">
         <v>912345678</v>
@@ -2549,18 +2255,18 @@
         <v>46</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>40</v>
@@ -2569,7 +2275,7 @@
         <v>41</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="G11" s="6">
         <v>912345679</v>
@@ -2578,33 +2284,33 @@
         <v>35866</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>46</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="D12" s="6">
         <v>123</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="G12" s="6">
         <v>987654321</v>
@@ -2613,7 +2319,7 @@
         <v>37143</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>46</v>
@@ -2624,22 +2330,22 @@
     </row>
     <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="G13" s="6">
         <v>987123456</v>
@@ -2654,27 +2360,27 @@
         <v>56</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="G14" s="6">
         <v>911111111</v>
@@ -2689,27 +2395,27 @@
         <v>46</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="G15" s="6">
         <v>922222222</v>
@@ -2718,7 +2424,7 @@
         <v>35285</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>46</v>
@@ -2729,22 +2435,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="G16" s="6">
         <v>933333333</v>
@@ -2753,7 +2459,7 @@
         <v>34803</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>56</v>
@@ -2764,31 +2470,31 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="H17" s="8">
         <v>37539</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>46</v>
@@ -2799,22 +2505,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="G18" s="6">
         <v>9876</v>
@@ -2823,7 +2529,7 @@
         <v>37622</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>56</v>
@@ -2834,22 +2540,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="G19" s="6">
         <v>123456789123</v>
@@ -2869,22 +2575,22 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="G20" s="6">
         <v>977777777</v>
@@ -2893,33 +2599,33 @@
         <v>35952</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>46</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="G21" s="6">
         <v>966666666</v>
@@ -2934,27 +2640,27 @@
         <v>46</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="G22" s="6">
         <v>955555555</v>
@@ -2969,27 +2675,27 @@
         <v>46</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="G23" s="6">
         <v>944444444</v>
@@ -2998,33 +2704,33 @@
         <v>36175</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>46</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>319</v>
+        <v>289</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="G24" s="6">
         <v>933333334</v>
@@ -3042,22 +2748,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="G25" s="6">
         <v>922222223</v>
@@ -3072,27 +2778,27 @@
         <v>46</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="G26" s="6">
         <v>911111112</v>
@@ -3110,22 +2816,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="G27" s="6">
         <v>900000000</v>
@@ -3143,22 +2849,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>155</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>339</v>
+        <v>309</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="G28" s="6">
         <v>988888888</v>
@@ -3167,7 +2873,7 @@
         <v>33436</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>46</v>
@@ -3178,22 +2884,22 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>346</v>
+        <v>316</v>
       </c>
       <c r="G29" s="6">
         <v>971234567</v>
@@ -3202,33 +2908,33 @@
         <v>36121</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>347</v>
+        <v>317</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="G30" s="6">
         <v>962345678</v>
@@ -3248,22 +2954,22 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>354</v>
+        <v>324</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="G31" s="6">
         <v>912340000</v>
@@ -3272,7 +2978,7 @@
         <v>36412</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>56</v>

--- a/DahlaFlowerShop/test/AutomationFramework/testdata/test_data.xlsx
+++ b/DahlaFlowerShop/test/AutomationFramework/testdata/test_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T14s-Gen1\Desktop\DATN\DahlaFlowerShop\test\AutomationFramework\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Desktop\DATN\DahlaFlowerShop\test\AutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B4B0B8-7BFC-4E09-A442-643323E189D6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07938E8-9532-46A8-9269-395C95EF58E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="347">
   <si>
     <t>id</t>
   </si>
@@ -1012,6 +1012,57 @@
   </si>
   <si>
     <t>TP.HCM</t>
+  </si>
+  <si>
+    <t>0912345679</t>
+  </si>
+  <si>
+    <t>0987123456</t>
+  </si>
+  <si>
+    <t>0911111111</t>
+  </si>
+  <si>
+    <t>0922222222</t>
+  </si>
+  <si>
+    <t>0933333333</t>
+  </si>
+  <si>
+    <t>0977777777</t>
+  </si>
+  <si>
+    <t>0966666666</t>
+  </si>
+  <si>
+    <t>0955555555</t>
+  </si>
+  <si>
+    <t>0944444444</t>
+  </si>
+  <si>
+    <t>0933333334</t>
+  </si>
+  <si>
+    <t>0922222223</t>
+  </si>
+  <si>
+    <t>0911111112</t>
+  </si>
+  <si>
+    <t>0900000000</t>
+  </si>
+  <si>
+    <t>0988888888</t>
+  </si>
+  <si>
+    <t>0971234567</t>
+  </si>
+  <si>
+    <t>0962345678</t>
+  </si>
+  <si>
+    <t>0912340000</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1110,13 +1161,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1423,7 +1477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -1431,7 +1485,7 @@
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1448,7 +1502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1465,7 +1519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -1480,7 +1534,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -1495,7 +1549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -1512,7 +1566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
@@ -1529,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -1542,7 +1596,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
@@ -1559,7 +1613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>26</v>
       </c>
@@ -1576,7 +1630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>154</v>
       </c>
@@ -1593,7 +1647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>157</v>
       </c>
@@ -1610,7 +1664,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>160</v>
       </c>
@@ -1627,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>162</v>
       </c>
@@ -1644,7 +1698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>164</v>
       </c>
@@ -1661,7 +1715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>166</v>
       </c>
@@ -1678,7 +1732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>168</v>
       </c>
@@ -1695,7 +1749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>170</v>
       </c>
@@ -1712,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>172</v>
       </c>
@@ -1729,7 +1783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>174</v>
       </c>
@@ -1746,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>176</v>
       </c>
@@ -1763,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>177</v>
       </c>
@@ -1780,7 +1834,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>180</v>
       </c>
@@ -1797,7 +1851,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>183</v>
       </c>
@@ -1814,7 +1868,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>184</v>
       </c>
@@ -1831,7 +1885,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>187</v>
       </c>
@@ -1848,7 +1902,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>191</v>
       </c>
@@ -1865,7 +1919,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>193</v>
       </c>
@@ -1882,7 +1936,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>196</v>
       </c>
@@ -1899,7 +1953,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>199</v>
       </c>
@@ -1924,7 +1978,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1938,7 +1992,7 @@
     <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1973,7 +2027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
@@ -2008,7 +2062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
@@ -2037,7 +2091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>52</v>
       </c>
@@ -2066,7 +2120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>57</v>
       </c>
@@ -2095,7 +2149,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>62</v>
       </c>
@@ -2124,7 +2178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>66</v>
       </c>
@@ -2153,7 +2207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>71</v>
       </c>
@@ -2188,7 +2242,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>80</v>
       </c>
@@ -2223,7 +2277,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>210</v>
       </c>
@@ -2242,8 +2296,8 @@
       <c r="F10" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G10" s="6">
-        <v>912345678</v>
+      <c r="G10" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="H10" s="8">
         <v>36290</v>
@@ -2258,7 +2312,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>215</v>
       </c>
@@ -2277,8 +2331,8 @@
       <c r="F11" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G11" s="6">
-        <v>912345679</v>
+      <c r="G11" s="9" t="s">
+        <v>330</v>
       </c>
       <c r="H11" s="8">
         <v>35866</v>
@@ -2293,7 +2347,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>221</v>
       </c>
@@ -2312,8 +2366,8 @@
       <c r="F12" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G12" s="6">
-        <v>987654321</v>
+      <c r="G12" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="H12" s="8">
         <v>37143</v>
@@ -2328,7 +2382,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>226</v>
       </c>
@@ -2347,8 +2401,8 @@
       <c r="F13" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="G13" s="6">
-        <v>987123456</v>
+      <c r="G13" s="9" t="s">
+        <v>331</v>
       </c>
       <c r="H13" s="8">
         <v>36728</v>
@@ -2363,7 +2417,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>233</v>
       </c>
@@ -2382,8 +2436,8 @@
       <c r="F14" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="G14" s="6">
-        <v>911111111</v>
+      <c r="G14" s="9" t="s">
+        <v>332</v>
       </c>
       <c r="H14" s="8">
         <v>35745</v>
@@ -2398,7 +2452,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>239</v>
       </c>
@@ -2417,8 +2471,8 @@
       <c r="F15" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="G15" s="6">
-        <v>922222222</v>
+      <c r="G15" s="9" t="s">
+        <v>333</v>
       </c>
       <c r="H15" s="8">
         <v>35285</v>
@@ -2433,7 +2487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>245</v>
       </c>
@@ -2452,8 +2506,8 @@
       <c r="F16" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G16" s="6">
-        <v>933333333</v>
+      <c r="G16" s="9" t="s">
+        <v>334</v>
       </c>
       <c r="H16" s="8">
         <v>34803</v>
@@ -2468,7 +2522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>251</v>
       </c>
@@ -2503,7 +2557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>258</v>
       </c>
@@ -2538,7 +2592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>264</v>
       </c>
@@ -2573,7 +2627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>269</v>
       </c>
@@ -2592,8 +2646,8 @@
       <c r="F20" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="G20" s="6">
-        <v>977777777</v>
+      <c r="G20" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="H20" s="8">
         <v>35952</v>
@@ -2608,7 +2662,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>274</v>
       </c>
@@ -2627,8 +2681,8 @@
       <c r="F21" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="G21" s="6">
-        <v>966666666</v>
+      <c r="G21" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="H21" s="8">
         <v>35692</v>
@@ -2643,7 +2697,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>278</v>
       </c>
@@ -2662,8 +2716,8 @@
       <c r="F22" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="G22" s="6">
-        <v>955555555</v>
+      <c r="G22" s="9" t="s">
+        <v>337</v>
       </c>
       <c r="H22" s="8">
         <v>36576</v>
@@ -2678,7 +2732,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>282</v>
       </c>
@@ -2697,8 +2751,8 @@
       <c r="F23" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="G23" s="6">
-        <v>944444444</v>
+      <c r="G23" s="9" t="s">
+        <v>338</v>
       </c>
       <c r="H23" s="8">
         <v>36175</v>
@@ -2713,7 +2767,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>287</v>
       </c>
@@ -2732,8 +2786,8 @@
       <c r="F24" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="G24" s="6">
-        <v>933333334</v>
+      <c r="G24" s="9" t="s">
+        <v>339</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6" t="s">
@@ -2746,7 +2800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>292</v>
       </c>
@@ -2765,8 +2819,8 @@
       <c r="F25" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="G25" s="6">
-        <v>922222223</v>
+      <c r="G25" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="H25" s="8">
         <v>49310</v>
@@ -2781,7 +2835,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>297</v>
       </c>
@@ -2800,8 +2854,8 @@
       <c r="F26" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G26" s="6">
-        <v>911111112</v>
+      <c r="G26" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="H26" s="8">
         <v>32998</v>
@@ -2814,7 +2868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>302</v>
       </c>
@@ -2833,8 +2887,8 @@
       <c r="F27" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="G27" s="6">
-        <v>900000000</v>
+      <c r="G27" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="H27" s="8">
         <v>34031</v>
@@ -2847,7 +2901,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>307</v>
       </c>
@@ -2866,8 +2920,8 @@
       <c r="F28" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="G28" s="6">
-        <v>988888888</v>
+      <c r="G28" s="9" t="s">
+        <v>343</v>
       </c>
       <c r="H28" s="8">
         <v>33436</v>
@@ -2882,7 +2936,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>311</v>
       </c>
@@ -2901,8 +2955,8 @@
       <c r="F29" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G29" s="6">
-        <v>971234567</v>
+      <c r="G29" s="9" t="s">
+        <v>344</v>
       </c>
       <c r="H29" s="8">
         <v>36121</v>
@@ -2917,7 +2971,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>318</v>
       </c>
@@ -2936,8 +2990,8 @@
       <c r="F30" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G30" s="6">
-        <v>962345678</v>
+      <c r="G30" s="9" t="s">
+        <v>345</v>
       </c>
       <c r="H30" s="8">
         <v>35234</v>
@@ -2952,7 +3006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>323</v>
       </c>
@@ -2971,8 +3025,8 @@
       <c r="F31" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="G31" s="6">
-        <v>912340000</v>
+      <c r="G31" s="9" t="s">
+        <v>346</v>
       </c>
       <c r="H31" s="8">
         <v>36412</v>
@@ -3017,7 +3071,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -3035,7 +3089,7 @@
     <col min="15" max="15" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3082,7 +3136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
@@ -3105,7 +3159,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>104</v>
       </c>
@@ -3136,7 +3190,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>109</v>
       </c>
@@ -3167,7 +3221,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>111</v>
       </c>
@@ -3198,7 +3252,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>115</v>
       </c>
@@ -3239,7 +3293,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>122</v>
       </c>
@@ -3272,7 +3326,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>126</v>
       </c>
@@ -3319,7 +3373,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>133</v>
       </c>
@@ -3360,7 +3414,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>138</v>
       </c>
@@ -3407,7 +3461,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>147</v>
       </c>
